--- a/data/trans_orig/IP22D4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Clase-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42117</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48073</t>
+          <t>48203</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93268</t>
+          <t>93284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>99396</t>
+          <t>99351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5301</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2798</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5214</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>78,65%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3689</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2082</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4085</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>50,96%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3927</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3945</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5883</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1289,107 +1289,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4125</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4134</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>77,56%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4350</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,64 +1632,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,64 +2088,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19880</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,64 +2544,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10575</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>13083</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,64 +3000,64 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,74 +3456,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>46888</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>42479</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>46003</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>42487</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>97,0%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>40849</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>37615</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>42264</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>89,0%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>51507</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>48203</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>52753</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>121</t>
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>97511</t>
+          <t>87737</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93284</t>
+          <t>83455</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>89523</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
